--- a/2027_plan.xlsx
+++ b/2027_plan.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="191">
   <si>
     <t xml:space="preserve">주차</t>
   </si>
@@ -32,42 +32,7 @@
     <t xml:space="preserve">D-Day</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">주초</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">월</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">주초(월)</t>
   </si>
   <si>
     <t xml:space="preserve">개요</t>
@@ -187,7 +152,7 @@
     <t xml:space="preserve">D-215</t>
   </si>
   <si>
-    <t xml:space="preserve">기출풀이 2023~2026 · 245~287차시 (24h50m)</t>
+    <t xml:space="preserve">기출풀이 2023~2026 · 245~295차시 (27h18m)</t>
   </si>
   <si>
     <t xml:space="preserve">W9</t>
@@ -660,72 +625,10 @@
     <t xml:space="preserve">Day</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">시험예정일 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">제</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">28</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">회</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">시험예정일 (제28회)</t>
   </si>
   <si>
     <t xml:space="preserve">월</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주초(월)</t>
   </si>
   <si>
     <t xml:space="preserve">2025-11</t>
@@ -1089,7 +992,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1110,10 +1013,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1122,28 +1021,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1166,7 +1053,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1470,7 +1357,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="1.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="46.47"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1487,656 +1374,651 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="6" t="n">
         <v>46237</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="6" t="n">
         <v>46244</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="6" t="n">
         <v>46251</v>
       </c>
       <c r="D4" s="4"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="6" t="n">
         <v>46258</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="10" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="6" t="n">
         <v>46265</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="6" t="n">
         <v>46272</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="6" t="n">
         <v>46279</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="10" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="6" t="n">
         <v>46286</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="10" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="6" t="n">
         <v>46293</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="6" t="n">
         <v>46300</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="9" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="6" t="n">
         <v>46307</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="10" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="6" t="n">
         <v>46314</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="10" t="s">
+      <c r="D13" s="10"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="6" t="n">
         <v>46321</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="10" t="s">
+      <c r="D14" s="10"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="6" t="n">
         <v>46328</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="6" t="n">
         <v>46335</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="10" t="s">
+      <c r="D16" s="11"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="6" t="n">
         <v>46342</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12" t="s">
+      <c r="D17" s="11"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="0" t="s">
+      <c r="I17" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="6" t="n">
         <v>46349</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="10" t="s">
+      <c r="D18" s="11"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="6" t="n">
         <v>46356</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="10" t="s">
+      <c r="D19" s="11"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="6" t="n">
         <v>46363</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="9" t="s">
+      <c r="D20" s="12"/>
+      <c r="E20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="6" t="n">
         <v>46370</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="10" t="s">
+      <c r="D21" s="12"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="6" t="n">
         <v>46377</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="10" t="s">
+      <c r="D22" s="12"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="6" t="n">
         <v>46384</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="10" t="s">
+      <c r="D23" s="12"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="6" t="n">
         <v>46391</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="10" t="s">
+      <c r="D24" s="12"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="6" t="n">
         <v>46398</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="10" t="s">
+      <c r="D25" s="12"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="6" t="n">
         <v>46405</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="13" t="s">
+      <c r="D26" s="13"/>
+      <c r="E26" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="6" t="n">
         <v>46412</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="10" t="s">
+      <c r="D27" s="13"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C28" s="6" t="n">
         <v>46419</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="10" t="s">
+      <c r="D28" s="13"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="6" t="n">
         <v>46426</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="10" t="s">
+      <c r="D29" s="13"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="6" t="n">
         <v>46433</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="10" t="s">
+      <c r="D30" s="13"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="6" t="n">
         <v>46440</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="10" t="s">
+      <c r="D31" s="13"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="6" t="n">
         <v>46447</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12" t="s">
+      <c r="D32" s="13"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="6" t="n">
         <v>46454</v>
       </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12" t="s">
+      <c r="D33" s="13"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="6" t="n">
         <v>46461</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="9" t="s">
+      <c r="D34" s="14"/>
+      <c r="E34" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="8" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C35" s="6" t="n">
         <v>46468</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12" t="s">
+      <c r="D35" s="14"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="8" t="n">
+      <c r="C36" s="6" t="n">
         <v>46475</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="10" t="s">
+      <c r="D36" s="14"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="6" t="n">
         <v>46482</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="10" t="s">
+      <c r="D37" s="14"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C38" s="6" t="n">
         <v>46489</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="10" t="s">
+      <c r="D38" s="14"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="6" t="n">
         <v>46496</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="9" t="s">
+      <c r="D39" s="8"/>
+      <c r="E39" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12" t="s">
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C40" s="6" t="n">
         <v>46501</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="19" t="s">
+      <c r="D40" s="8"/>
+      <c r="E40" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="F40" s="8"/>
+    </row>
     <row r="1048566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2177,39 +2059,39 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>131</v>
-      </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>132</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="22" t="n">
+      <c r="C2" s="18" t="n">
         <v>45964</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="22" t="n">
+      <c r="C3" s="18" t="n">
         <v>45971</v>
       </c>
     </row>
@@ -2217,319 +2099,319 @@
       <c r="B4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="19" t="n">
         <v>45978</v>
       </c>
-      <c r="D4" s="24"/>
+      <c r="D4" s="20"/>
       <c r="H4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="1" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>45985</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="F5" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>45985</v>
-      </c>
-      <c r="D5" s="24"/>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="1" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>137</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="18" t="n">
         <v>45992</v>
       </c>
-      <c r="D6" s="24"/>
+      <c r="D6" s="20"/>
       <c r="F6" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>45999</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="F7" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>45999</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="F7" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="18" t="n">
         <v>46006</v>
       </c>
-      <c r="D8" s="24"/>
+      <c r="D8" s="20"/>
       <c r="F8" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>46013</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="F9" s="1" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <v>46013</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="F9" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="18" t="n">
         <v>46020</v>
       </c>
-      <c r="D10" s="24"/>
+      <c r="D10" s="20"/>
       <c r="F10" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="18" t="n">
         <v>46027</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="18" t="n">
         <v>46034</v>
       </c>
-      <c r="D12" s="24"/>
+      <c r="D12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="18" t="n">
         <v>46041</v>
       </c>
-      <c r="D13" s="24"/>
+      <c r="D13" s="20"/>
       <c r="H13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="18" t="n">
         <v>46048</v>
       </c>
-      <c r="D14" s="25"/>
+      <c r="D14" s="21"/>
       <c r="F14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H14" s="1" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+      <c r="B15" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>46055</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="F15" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>46055</v>
-      </c>
-      <c r="D15" s="25"/>
-      <c r="F15" s="1" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="18" t="n">
         <v>46062</v>
       </c>
-      <c r="D16" s="25"/>
+      <c r="D16" s="21"/>
       <c r="F16" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D17" s="21"/>
+      <c r="G17" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>46069</v>
-      </c>
-      <c r="D17" s="25"/>
-      <c r="G17" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="18" t="n">
         <v>46076</v>
       </c>
-      <c r="D18" s="25"/>
+      <c r="D18" s="21"/>
       <c r="F18" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="B19" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="F19" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="22" t="n">
-        <v>46083</v>
-      </c>
-      <c r="D19" s="25"/>
-      <c r="F19" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="18" t="n">
         <v>46090</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="22"/>
       <c r="H20" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21" t="s">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="18" t="n">
         <v>46097</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="18" t="n">
         <v>46104</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="18" t="n">
         <v>46111</v>
       </c>
-      <c r="D23" s="26"/>
+      <c r="D23" s="22"/>
       <c r="E23" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
-        <v>157</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="18" t="n">
         <v>46118</v>
       </c>
-      <c r="D24" s="27"/>
+      <c r="D24" s="23"/>
       <c r="H24" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I24" s="1" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D25" s="23"/>
+      <c r="H25" s="1" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>46125</v>
-      </c>
-      <c r="D25" s="27"/>
-      <c r="H25" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="18" t="n">
         <v>46132</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="1" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>46137</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20" t="s">
         <v>162</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="29" t="n">
-        <v>46137</v>
-      </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="1048566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2571,486 +2453,486 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="18" t="n">
+        <v>42653</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="22" t="n">
-        <v>42653</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="22" t="n">
+      <c r="C3" s="18" t="n">
         <v>42660</v>
       </c>
-      <c r="D3" s="25"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F3" s="1" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>42667</v>
+      </c>
+      <c r="D4" s="21"/>
+      <c r="E4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="22" t="n">
-        <v>42667</v>
-      </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="18" t="n">
         <v>42674</v>
       </c>
-      <c r="D5" s="25"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="1" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="B6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>42681</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="F6" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>42681</v>
-      </c>
-      <c r="D6" s="25"/>
-      <c r="F6" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="18" t="n">
         <v>42688</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="18" t="n">
         <v>42695</v>
       </c>
-      <c r="D8" s="24"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="18" t="n">
         <v>42702</v>
       </c>
-      <c r="D9" s="24"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="B10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>42709</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="F10" s="1" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>42709</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="F10" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="18" t="n">
         <v>42716</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="20"/>
       <c r="F11" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>42723</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="F12" s="1" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>42723</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="F12" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="18" t="n">
         <v>42730</v>
       </c>
-      <c r="D13" s="24"/>
+      <c r="D13" s="20"/>
       <c r="F13" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>42737</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="F14" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>42737</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="F14" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="18" t="n">
         <v>42744</v>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="18" t="n">
         <v>42751</v>
       </c>
-      <c r="D16" s="24"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="18" t="n">
         <v>42758</v>
       </c>
-      <c r="D17" s="24"/>
+      <c r="D17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="18" t="n">
         <v>42765</v>
       </c>
-      <c r="D18" s="25"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
         <v>178</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>179</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="18" t="n">
         <v>42772</v>
       </c>
-      <c r="D19" s="25"/>
+      <c r="D19" s="21"/>
       <c r="F19" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>42779</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="F20" s="1" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>42779</v>
-      </c>
-      <c r="D20" s="25"/>
-      <c r="F20" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="18" t="n">
         <v>42786</v>
       </c>
-      <c r="D21" s="25"/>
+      <c r="D21" s="21"/>
       <c r="F21" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>42793</v>
+      </c>
+      <c r="D22" s="21"/>
+      <c r="F22" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>42793</v>
-      </c>
-      <c r="D22" s="25"/>
-      <c r="F22" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>180</v>
+      <c r="A23" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="18" t="n">
         <v>42800</v>
       </c>
-      <c r="D23" s="25"/>
+      <c r="D23" s="21"/>
       <c r="F23" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="18" t="n">
         <v>42807</v>
       </c>
-      <c r="D24" s="25"/>
+      <c r="D24" s="21"/>
       <c r="F24" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="18" t="n">
         <v>42814</v>
       </c>
-      <c r="D25" s="25"/>
+      <c r="D25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="18" t="n">
         <v>42821</v>
       </c>
-      <c r="D26" s="25"/>
+      <c r="D26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
-        <v>181</v>
+      <c r="A27" s="17" t="s">
+        <v>180</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="18" t="n">
         <v>42828</v>
       </c>
-      <c r="D27" s="25"/>
+      <c r="D27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21" t="s">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="18" t="n">
         <v>42835</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="20"/>
       <c r="E28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="18" t="n">
         <v>42842</v>
       </c>
-      <c r="D29" s="24"/>
+      <c r="D29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="22" t="n">
+      <c r="C30" s="18" t="n">
         <v>42849</v>
       </c>
-      <c r="D30" s="27"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F30" s="1" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
-        <v>186</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="18" t="n">
         <v>42856</v>
       </c>
-      <c r="D31" s="27"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21" t="s">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="18" t="n">
         <v>42863</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="18" t="n">
         <v>42870</v>
       </c>
-      <c r="D33" s="27"/>
+      <c r="D33" s="23"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="18" t="n">
         <v>42877</v>
       </c>
-      <c r="D34" s="27"/>
+      <c r="D34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="18" t="n">
         <v>42884</v>
       </c>
-      <c r="D35" s="27"/>
+      <c r="D35" s="23"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B36" s="21" t="s">
+      <c r="A36" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="22" t="n">
+      <c r="C36" s="18" t="n">
         <v>42891</v>
       </c>
-      <c r="D36" s="27"/>
+      <c r="D36" s="23"/>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="22" t="n">
+      <c r="C37" s="18" t="n">
         <v>42898</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>42903</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24" t="s">
-        <v>163</v>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3081,488 +2963,488 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="18" t="n">
+        <v>42652</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="22" t="n">
-        <v>42652</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="22" t="n">
+      <c r="C3" s="18" t="n">
         <v>42659</v>
       </c>
-      <c r="D3" s="25"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="18" t="n">
         <v>42666</v>
       </c>
-      <c r="D4" s="25"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="18" t="n">
         <v>42673</v>
       </c>
-      <c r="D5" s="25"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="1" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="B6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>42680</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="F6" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>42680</v>
-      </c>
-      <c r="D6" s="25"/>
-      <c r="F6" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="18" t="n">
         <v>42687</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="18" t="n">
         <v>42694</v>
       </c>
-      <c r="D8" s="24"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="18" t="n">
         <v>42701</v>
       </c>
-      <c r="D9" s="24"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="B10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>42708</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="F10" s="1" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>42708</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="F10" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="18" t="n">
         <v>42715</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="20"/>
       <c r="F11" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>42722</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="F12" s="1" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>42722</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="F12" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="18" t="n">
         <v>42729</v>
       </c>
-      <c r="D13" s="24"/>
+      <c r="D13" s="20"/>
       <c r="F13" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>42736</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="F14" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>42736</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="F14" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="18" t="n">
         <v>42743</v>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="18" t="n">
         <v>42751</v>
       </c>
-      <c r="D16" s="24"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="18" t="n">
         <v>42757</v>
       </c>
-      <c r="D17" s="24"/>
+      <c r="D17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="18" t="n">
         <v>42764</v>
       </c>
-      <c r="D18" s="25"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>179</v>
+      <c r="A19" s="17" t="s">
+        <v>178</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="18" t="n">
         <v>42771</v>
       </c>
-      <c r="D19" s="25"/>
+      <c r="D19" s="21"/>
       <c r="F19" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>42778</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="F20" s="1" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>42778</v>
-      </c>
-      <c r="D20" s="25"/>
-      <c r="F20" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="18" t="n">
         <v>42785</v>
       </c>
-      <c r="D21" s="25"/>
+      <c r="D21" s="21"/>
       <c r="F21" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>42792</v>
+      </c>
+      <c r="D22" s="21"/>
+      <c r="F22" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>42792</v>
-      </c>
-      <c r="D22" s="25"/>
-      <c r="F22" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>180</v>
+      <c r="A23" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="18" t="n">
         <v>42799</v>
       </c>
-      <c r="D23" s="25"/>
+      <c r="D23" s="21"/>
       <c r="F23" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="18" t="n">
         <v>42806</v>
       </c>
-      <c r="D24" s="25"/>
+      <c r="D24" s="21"/>
       <c r="F24" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="18" t="n">
         <v>42813</v>
       </c>
-      <c r="D25" s="25"/>
+      <c r="D25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="18" t="n">
         <v>42820</v>
       </c>
-      <c r="D26" s="25"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
-        <v>181</v>
+      <c r="A27" s="17" t="s">
+        <v>180</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="18" t="n">
         <v>42827</v>
       </c>
-      <c r="D27" s="25"/>
+      <c r="D27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21" t="s">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="18" t="n">
         <v>42844</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="20"/>
       <c r="E28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="18" t="n">
         <v>42841</v>
       </c>
-      <c r="D29" s="24"/>
+      <c r="D29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="22" t="n">
+      <c r="C30" s="18" t="n">
         <v>42848</v>
       </c>
-      <c r="D30" s="27"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="18" t="n">
         <v>42855</v>
       </c>
-      <c r="D31" s="27"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="B32" s="21" t="s">
+      <c r="A32" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="18" t="n">
         <v>42862</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="18" t="n">
         <v>42869</v>
       </c>
-      <c r="D33" s="27"/>
+      <c r="D33" s="23"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="18" t="n">
         <v>42876</v>
       </c>
-      <c r="D34" s="27"/>
+      <c r="D34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="18" t="n">
         <v>42883</v>
       </c>
-      <c r="D35" s="27"/>
+      <c r="D35" s="23"/>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B36" s="21" t="s">
+      <c r="A36" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="22" t="n">
+      <c r="C36" s="18" t="n">
         <v>42890</v>
       </c>
-      <c r="D36" s="27"/>
+      <c r="D36" s="23"/>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="22" t="n">
+      <c r="C37" s="18" t="n">
         <v>42897</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>42902</v>
       </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24" t="s">
-        <v>163</v>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
